--- a/src/assets/excel/PSG_template-payslip.xlsx
+++ b/src/assets/excel/PSG_template-payslip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\PROJECT\gbvh\gbvh\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5397F162-B7E6-4EE0-BBCF-C964C298B4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89461F73-CB90-41E4-8B4B-6E3F71C28075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>NIK</t>
   </si>
@@ -136,6 +136,18 @@
   </si>
   <si>
     <t>PENGEMBALIAN_PPH</t>
+  </si>
+  <si>
+    <t>OT_Libur_1</t>
+  </si>
+  <si>
+    <t>OT_Libur_2</t>
+  </si>
+  <si>
+    <t>OT_Hari_Libur_1</t>
+  </si>
+  <si>
+    <t>OT_Hari_Libur_2</t>
   </si>
 </sst>
 </file>
@@ -557,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C86984-557A-49A9-B90A-6FD29497B13B}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.6640625" customWidth="1"/>
@@ -573,7 +585,7 @@
     <col min="37" max="37" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>32</v>
       </c>
@@ -631,58 +643,70 @@
       <c r="S1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="X1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="Y1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AH1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AI1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AL1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AM1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AJ1" s="8" t="s">
+      <c r="AN1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="AO1" s="5" t="s">
         <v>31</v>
       </c>
     </row>
